--- a/week5-stata2/qy111_stata2/qy111_Dataset_IDcard.xlsx
+++ b/week5-stata2/qy111_stata2/qy111_Dataset_IDcard.xlsx
@@ -1,27 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bl517/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f66ff72783ca365e/Experimental Design/Peer Review 2/ppol6818-spring2026/week5-stata2/qy111_stata2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFFA0A85-96A6-7443-B63A-B9CCA7E852DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{AFFA0A85-96A6-7443-B63A-B9CCA7E852DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F41C7BEE-6D01-4B8F-942E-F1FCDB6531D5}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12110" yWindow="2310" windowWidth="15870" windowHeight="16470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Blank" sheetId="1" r:id="rId1"/>
-    <sheet name="Sample" sheetId="2" r:id="rId2"/>
+    <sheet name="Q1" sheetId="5" r:id="rId1"/>
+    <sheet name="Q2" sheetId="6" r:id="rId2"/>
+    <sheet name="Q3" sheetId="8" r:id="rId3"/>
+    <sheet name="Q4" sheetId="9" r:id="rId4"/>
+    <sheet name="Q5" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="17">
   <si>
     <t>Dataset ID card</t>
   </si>
@@ -73,84 +76,12 @@
   <si>
     <t>Name</t>
   </si>
-  <si>
-    <t>week3/q1/households.dta</t>
-  </si>
-  <si>
-    <t>Household</t>
-  </si>
-  <si>
-    <t>2 mismatches w sample</t>
-  </si>
-  <si>
-    <t>hhid</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>Metadata</t>
-  </si>
-  <si>
-    <t>enum, length, etc.</t>
-  </si>
-  <si>
-    <t>Demographics</t>
-  </si>
-  <si>
-    <t>GPS, ages, gender</t>
-  </si>
-  <si>
-    <t>many missing values in GPS</t>
-  </si>
-  <si>
-    <t>Finances</t>
-  </si>
-  <si>
-    <t>inc_*, savings_*, debt_*</t>
-  </si>
-  <si>
-    <t>non numeric vars to clean</t>
-  </si>
-  <si>
-    <t>Opinions</t>
-  </si>
-  <si>
-    <t>pol_*</t>
-  </si>
-  <si>
-    <t>Time use</t>
-  </si>
-  <si>
-    <t>time_*</t>
-  </si>
-  <si>
-    <t>at the member level</t>
-  </si>
-  <si>
-    <t>Members</t>
-  </si>
-  <si>
-    <t>demographic, time use</t>
-  </si>
-  <si>
-    <t>in wide format, up to 10 per hhid</t>
-  </si>
-  <si>
-    <t>District</t>
-  </si>
-  <si>
-    <t>geographic info</t>
-  </si>
-  <si>
-    <t>repeated across rows</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -183,6 +114,13 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -508,31 +446,31 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -748,23 +686,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A2:H35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C15CA417-BB7F-4CED-92A5-972148C83C05}">
+  <dimension ref="A1:H35"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.5" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" customWidth="1"/>
-    <col min="4" max="5" width="8.83203125" customWidth="1"/>
-    <col min="6" max="6" width="13.83203125" customWidth="1"/>
+    <col min="1" max="1" width="5.453125" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" customWidth="1"/>
+    <col min="3" max="3" width="11.6328125" customWidth="1"/>
+    <col min="4" max="5" width="8.81640625" customWidth="1"/>
+    <col min="6" max="6" width="13.81640625" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="4.5" customWidth="1"/>
+    <col min="8" max="8" width="4.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="13" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:8" ht="17" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -776,56 +712,56 @@
       <c r="G2" s="3"/>
       <c r="H2" s="4"/>
     </row>
-    <row r="3" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="27" t="s">
+    <row r="3" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="29"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="36"/>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="G4" s="6"/>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="8"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="29"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C5" s="43"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="36"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="G6" s="6"/>
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
-      <c r="D7" s="31" t="s">
+      <c r="D7" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
       <c r="G7" s="11"/>
       <c r="H7" s="4"/>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="32"/>
-      <c r="B8" s="28"/>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="45"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="4"/>
       <c r="D8" s="12" t="s">
         <v>5</v>
@@ -833,19 +769,19 @@
       <c r="E8" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="33" t="s">
+      <c r="F8" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="G8" s="34"/>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G8" s="40"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="D9" s="14"/>
       <c r="E9" s="15"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="36"/>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F9" s="37"/>
+      <c r="G9" s="38"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="D10" s="17"/>
@@ -853,7 +789,7 @@
       <c r="G10" s="6"/>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>8</v>
       </c>
@@ -865,7 +801,7 @@
       <c r="G11" s="18"/>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
       <c r="B12" s="17" t="s">
         <v>9</v>
@@ -876,25 +812,25 @@
       <c r="E12" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="37" t="s">
+      <c r="F12" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="34"/>
+      <c r="G12" s="40"/>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="9"/>
       <c r="D13" s="14"/>
       <c r="E13" s="15"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="36"/>
-    </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F13" s="41"/>
+      <c r="G13" s="38"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="16"/>
       <c r="G14" s="6"/>
     </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>12</v>
       </c>
@@ -905,103 +841,103 @@
       <c r="F15" s="8"/>
       <c r="G15" s="18"/>
     </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
       <c r="B16" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="39" t="s">
+      <c r="C16" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="28"/>
-      <c r="E16" s="39" t="s">
+      <c r="D16" s="34"/>
+      <c r="E16" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="F16" s="28"/>
-      <c r="G16" s="29"/>
-    </row>
-    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F16" s="34"/>
+      <c r="G16" s="36"/>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
       <c r="B17" s="19"/>
-      <c r="C17" s="40"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="42"/>
-    </row>
-    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C17" s="27"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="29"/>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="20"/>
-      <c r="C18" s="40"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="45"/>
-    </row>
-    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C18" s="27"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="32"/>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="20"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="45"/>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C19" s="27"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="32"/>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
       <c r="B20" s="20"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="45"/>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C20" s="27"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="32"/>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
       <c r="B21" s="20"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="45"/>
-    </row>
-    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C21" s="27"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="32"/>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="B22" s="20"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="45"/>
-    </row>
-    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C22" s="27"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="32"/>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="B23" s="20"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="45"/>
-    </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C23" s="27"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="32"/>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="B24" s="20"/>
-      <c r="C24" s="40"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="45"/>
-    </row>
-    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C24" s="27"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="32"/>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
       <c r="B25" s="20"/>
-      <c r="C25" s="40"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="43"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="45"/>
-    </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C25" s="27"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="32"/>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
       <c r="B26" s="21"/>
       <c r="C26" s="21"/>
@@ -1010,13 +946,13 @@
       <c r="F26" s="21"/>
       <c r="G26" s="22"/>
     </row>
-    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="29"/>
-    </row>
-    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E27" s="35"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="36"/>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>15</v>
       </c>
@@ -1027,31 +963,31 @@
       <c r="F28" s="8"/>
       <c r="G28" s="18"/>
     </row>
-    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C29" s="39" t="s">
+      <c r="C29" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D29" s="28"/>
-      <c r="E29" s="39" t="s">
+      <c r="D29" s="34"/>
+      <c r="E29" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="F29" s="28"/>
-      <c r="G29" s="29"/>
-    </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F29" s="34"/>
+      <c r="G29" s="36"/>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
       <c r="B30" s="19"/>
       <c r="C30" s="19"/>
       <c r="D30" s="19"/>
-      <c r="E30" s="40"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="42"/>
-    </row>
-    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E30" s="27"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="29"/>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
       <c r="B31" s="20"/>
       <c r="C31" s="20"/>
@@ -1060,7 +996,7 @@
       <c r="F31" s="20"/>
       <c r="G31" s="23"/>
     </row>
-    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
       <c r="B32" s="20"/>
       <c r="C32" s="20"/>
@@ -1069,7 +1005,7 @@
       <c r="F32" s="20"/>
       <c r="G32" s="23"/>
     </row>
-    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
       <c r="B33" s="20"/>
       <c r="C33" s="20"/>
@@ -1078,7 +1014,7 @@
       <c r="F33" s="20"/>
       <c r="G33" s="23"/>
     </row>
-    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
       <c r="B34" s="21"/>
       <c r="C34" s="21"/>
@@ -1087,7 +1023,7 @@
       <c r="F34" s="21"/>
       <c r="G34" s="22"/>
     </row>
-    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="24"/>
       <c r="B35" s="25"/>
       <c r="C35" s="25"/>
@@ -1099,60 +1035,59 @@
   </sheetData>
   <mergeCells count="32">
     <mergeCell ref="E30:G30"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:G18"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="E19:G19"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="E20:G20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="E27:G27"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="F9:G9"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="E16:G16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:G17"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A2:H35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B948FA17-3D0E-4890-B49B-EE6ECBCC8972}">
+  <dimension ref="A1:H35"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.5" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" customWidth="1"/>
-    <col min="4" max="5" width="8.83203125" customWidth="1"/>
-    <col min="6" max="6" width="13.83203125" customWidth="1"/>
+    <col min="1" max="1" width="5.453125" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" customWidth="1"/>
+    <col min="3" max="3" width="11.6328125" customWidth="1"/>
+    <col min="4" max="5" width="8.81640625" customWidth="1"/>
+    <col min="6" max="6" width="13.81640625" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="4.5" customWidth="1"/>
+    <col min="8" max="8" width="4.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="13" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:8" ht="17" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1164,60 +1099,56 @@
       <c r="G2" s="3"/>
       <c r="H2" s="4"/>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="27" t="s">
+    <row r="3" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="29"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="36"/>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="G4" s="6"/>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="8"/>
-      <c r="C5" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="29"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C5" s="43"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="36"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="G6" s="6"/>
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
-      <c r="D7" s="31" t="s">
+      <c r="D7" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
       <c r="G7" s="11"/>
       <c r="H7" s="4"/>
     </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="28"/>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="45"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="4"/>
       <c r="D8" s="12" t="s">
         <v>5</v>
@@ -1225,25 +1156,19 @@
       <c r="E8" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="33" t="s">
+      <c r="F8" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="G8" s="34"/>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G8" s="40"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
-      <c r="D9" s="14">
-        <v>100</v>
-      </c>
-      <c r="E9" s="15">
-        <v>98</v>
-      </c>
-      <c r="F9" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="36"/>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D9" s="14"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="38"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="D10" s="17"/>
@@ -1251,7 +1176,7 @@
       <c r="G10" s="6"/>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>8</v>
       </c>
@@ -1263,7 +1188,7 @@
       <c r="G11" s="18"/>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
       <c r="B12" s="17" t="s">
         <v>9</v>
@@ -1274,32 +1199,25 @@
       <c r="E12" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="37" t="s">
+      <c r="F12" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="34"/>
+      <c r="G12" s="40"/>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
-      <c r="B13" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="15">
-        <v>98</v>
-      </c>
-      <c r="F13" s="38"/>
-      <c r="G13" s="36"/>
-    </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B13" s="9"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="38"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="16"/>
       <c r="G14" s="6"/>
     </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>12</v>
       </c>
@@ -1310,129 +1228,103 @@
       <c r="F15" s="8"/>
       <c r="G15" s="18"/>
     </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
       <c r="B16" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="39" t="s">
+      <c r="C16" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="28"/>
-      <c r="E16" s="39" t="s">
+      <c r="D16" s="34"/>
+      <c r="E16" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="F16" s="28"/>
-      <c r="G16" s="29"/>
-    </row>
-    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F16" s="34"/>
+      <c r="G16" s="36"/>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
-      <c r="B17" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="41"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="42"/>
-    </row>
-    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B17" s="19"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="29"/>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
-      <c r="B18" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="41"/>
-      <c r="E18" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="F18" s="44"/>
-      <c r="G18" s="45"/>
-    </row>
-    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="20"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="32"/>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
-      <c r="B19" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" s="41"/>
-      <c r="E19" s="43" t="s">
-        <v>29</v>
-      </c>
-      <c r="F19" s="44"/>
-      <c r="G19" s="45"/>
-    </row>
-    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B19" s="20"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="32"/>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
-      <c r="B20" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="C20" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="D20" s="41"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="45"/>
-    </row>
-    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B20" s="20"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="32"/>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
-      <c r="B21" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="D21" s="41"/>
-      <c r="E21" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="F21" s="44"/>
-      <c r="G21" s="45"/>
-    </row>
-    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B21" s="20"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="32"/>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="B22" s="20"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="45"/>
-    </row>
-    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C22" s="27"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="32"/>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="B23" s="20"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="45"/>
-    </row>
-    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C23" s="27"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="32"/>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="B24" s="20"/>
-      <c r="C24" s="40"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="44"/>
-      <c r="G24" s="45"/>
-    </row>
-    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C24" s="27"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="32"/>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
       <c r="B25" s="20"/>
-      <c r="C25" s="40"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="43"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="45"/>
-    </row>
-    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C25" s="27"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="32"/>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
       <c r="B26" s="21"/>
       <c r="C26" s="21"/>
@@ -1441,13 +1333,13 @@
       <c r="F26" s="21"/>
       <c r="G26" s="22"/>
     </row>
-    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="29"/>
-    </row>
-    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E27" s="35"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="36"/>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>15</v>
       </c>
@@ -1458,52 +1350,40 @@
       <c r="F28" s="8"/>
       <c r="G28" s="18"/>
     </row>
-    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C29" s="39" t="s">
+      <c r="C29" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D29" s="28"/>
-      <c r="E29" s="39" t="s">
+      <c r="D29" s="34"/>
+      <c r="E29" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="F29" s="28"/>
-      <c r="G29" s="29"/>
-    </row>
-    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F29" s="34"/>
+      <c r="G29" s="36"/>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
-      <c r="B30" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>36</v>
-      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
       <c r="D30" s="19"/>
-      <c r="E30" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="F30" s="41"/>
-      <c r="G30" s="42"/>
-    </row>
-    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E30" s="27"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="29"/>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
-      <c r="B31" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>39</v>
-      </c>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
       <c r="D31" s="20"/>
-      <c r="E31" s="20" t="s">
-        <v>40</v>
-      </c>
+      <c r="E31" s="20"/>
       <c r="F31" s="20"/>
       <c r="G31" s="23"/>
     </row>
-    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
       <c r="B32" s="20"/>
       <c r="C32" s="20"/>
@@ -1512,7 +1392,7 @@
       <c r="F32" s="20"/>
       <c r="G32" s="23"/>
     </row>
-    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
       <c r="B33" s="20"/>
       <c r="C33" s="20"/>
@@ -1521,7 +1401,7 @@
       <c r="F33" s="20"/>
       <c r="G33" s="23"/>
     </row>
-    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
       <c r="B34" s="21"/>
       <c r="C34" s="21"/>
@@ -1530,7 +1410,7 @@
       <c r="F34" s="21"/>
       <c r="G34" s="22"/>
     </row>
-    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="24"/>
       <c r="B35" s="25"/>
       <c r="C35" s="25"/>
@@ -1542,38 +1422,1201 @@
   </sheetData>
   <mergeCells count="32">
     <mergeCell ref="E30:G30"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:G18"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="E19:G19"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="E20:G20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="E27:G27"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="F9:G9"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="E16:G16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:G17"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="C5:G5"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C5E97B4-DA73-42B2-BB29-00D5ADA61909}">
+  <dimension ref="A1:H35"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.453125" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" customWidth="1"/>
+    <col min="3" max="3" width="11.6328125" customWidth="1"/>
+    <col min="4" max="5" width="8.81640625" customWidth="1"/>
+    <col min="6" max="6" width="13.81640625" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="4.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="13" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:8" ht="17" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="36"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="45"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="40"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="38"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="16"/>
+      <c r="B10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
+      <c r="B12" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="40"/>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="9"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="38"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="16"/>
+      <c r="G14" s="6"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="18"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5"/>
+      <c r="B16" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="34"/>
+      <c r="E16" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" s="34"/>
+      <c r="G16" s="36"/>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="5"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="29"/>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="5"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="32"/>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="5"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="32"/>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="5"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="32"/>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="32"/>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="32"/>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="32"/>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="5"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="32"/>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="5"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="32"/>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="22"/>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="5"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="36"/>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="10"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="18"/>
+    </row>
+    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="5"/>
+      <c r="B29" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="34"/>
+      <c r="E29" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" s="34"/>
+      <c r="G29" s="36"/>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="5"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="29"/>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="5"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="23"/>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="5"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="23"/>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="5"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="23"/>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="5"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="22"/>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="24"/>
+      <c r="B35" s="25"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="26"/>
+    </row>
+  </sheetData>
+  <mergeCells count="32">
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+  </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7910FAE4-CEC4-41A6-9519-D7546C9F6B1B}">
+  <dimension ref="A1:H35"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.453125" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" customWidth="1"/>
+    <col min="3" max="3" width="11.6328125" customWidth="1"/>
+    <col min="4" max="5" width="8.81640625" customWidth="1"/>
+    <col min="6" max="6" width="13.81640625" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="4.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="13" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:8" ht="17" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="36"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="45"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="40"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="38"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="16"/>
+      <c r="B10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
+      <c r="B12" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="40"/>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="9"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="38"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="16"/>
+      <c r="G14" s="6"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="18"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5"/>
+      <c r="B16" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="34"/>
+      <c r="E16" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" s="34"/>
+      <c r="G16" s="36"/>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="5"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="29"/>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="5"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="32"/>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="5"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="32"/>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="5"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="32"/>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="32"/>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="32"/>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="32"/>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="5"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="32"/>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="5"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="32"/>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="22"/>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="5"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="36"/>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="10"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="18"/>
+    </row>
+    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="5"/>
+      <c r="B29" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="34"/>
+      <c r="E29" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" s="34"/>
+      <c r="G29" s="36"/>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="5"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="29"/>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="5"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="23"/>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="5"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="23"/>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="5"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="23"/>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="5"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="22"/>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="24"/>
+      <c r="B35" s="25"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="26"/>
+    </row>
+  </sheetData>
+  <mergeCells count="32">
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+  </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C45A1B1-839C-491F-8A0D-546F9A1B35E5}">
+  <dimension ref="A1:H35"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.453125" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" customWidth="1"/>
+    <col min="3" max="3" width="11.6328125" customWidth="1"/>
+    <col min="4" max="5" width="8.81640625" customWidth="1"/>
+    <col min="6" max="6" width="13.81640625" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="4.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="13" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:8" ht="17" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3" spans="1:8" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="36"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="45"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="40"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="38"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="16"/>
+      <c r="B10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
+      <c r="B12" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="40"/>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="9"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="38"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="16"/>
+      <c r="G14" s="6"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="18"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5"/>
+      <c r="B16" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="34"/>
+      <c r="E16" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" s="34"/>
+      <c r="G16" s="36"/>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="5"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="29"/>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="5"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="32"/>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="5"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="32"/>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="5"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="32"/>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="32"/>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="32"/>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="32"/>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="5"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="32"/>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="5"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="32"/>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="22"/>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="5"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="36"/>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="10"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="18"/>
+    </row>
+    <row r="29" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="5"/>
+      <c r="B29" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="34"/>
+      <c r="E29" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" s="34"/>
+      <c r="G29" s="36"/>
+    </row>
+    <row r="30" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="5"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="29"/>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="5"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="23"/>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="5"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="23"/>
+    </row>
+    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="5"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="23"/>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="5"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="22"/>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="24"/>
+      <c r="B35" s="25"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="26"/>
+    </row>
+  </sheetData>
+  <mergeCells count="32">
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="F9:G9"/>
+  </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>